--- a/Raw Materials/Vulcanization/성형공정_제약조건.xlsx
+++ b/Raw Materials/Vulcanization/성형공정_제약조건.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SWI\통합계획\클로드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Check_In_Service\Extrusion_Vulcanization_Scheduling_System\Raw Materials\Vulcanization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B49AFAE-DF57-4D5D-89AD-6D7CD24B8DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F2A8E265-CF04-4D2D-B7BD-04B0FE4810B2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="94">
   <si>
     <t>HOSE</t>
   </si>
@@ -309,9 +308,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>25474-2S000/2S010</t>
-  </si>
-  <si>
     <t>28415-08400</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -336,10 +332,6 @@
     <t>A 672 203 20 02</t>
   </si>
   <si>
-    <t>25475-07201-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>25482-07TA0</t>
   </si>
   <si>
@@ -359,13 +351,25 @@
   </si>
   <si>
     <t>\</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25474-2S010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25474-2S000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25475-07201</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -852,9 +856,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790A88E3-97BA-4B56-9AAE-0A981A51B651}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:T48"/>
+  <dimension ref="A2:T49"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
@@ -2264,7 +2268,7 @@
         <v>12</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>11</v>
@@ -2522,7 +2526,7 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="6" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B35" s="6">
         <v>11</v>
@@ -2569,62 +2573,66 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B36" s="6">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C36" s="6">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="D36" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E36" s="6">
-        <v>5</v>
-      </c>
-      <c r="F36" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="F36" s="6">
+        <v>7</v>
+      </c>
       <c r="G36" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K36" s="6">
-        <v>0</v>
-      </c>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="L36" s="6">
+        <v>4</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O36" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B37" s="6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C37" s="6">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D37" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E37" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6" t="s">
@@ -2640,24 +2648,22 @@
         <v>11</v>
       </c>
       <c r="K37" s="6">
-        <v>20</v>
-      </c>
-      <c r="L37" s="6">
-        <v>1</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B38" s="6">
         <v>7</v>
@@ -2702,13 +2708,13 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B39" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C39" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D39" s="6">
         <v>1</v>
@@ -2747,7 +2753,7 @@
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B40" s="6">
         <v>9</v>
@@ -2792,7 +2798,7 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B41" s="6">
         <v>9</v>
@@ -2801,7 +2807,7 @@
         <v>20</v>
       </c>
       <c r="D41" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="6">
         <v>0</v>
@@ -2837,7 +2843,7 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B42" s="6">
         <v>9</v>
@@ -2881,17 +2887,17 @@
       </c>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43" s="9" t="s">
-        <v>86</v>
+      <c r="A43" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="B43" s="6">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="D43" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="6">
         <v>0</v>
@@ -2910,93 +2916,93 @@
         <v>11</v>
       </c>
       <c r="K43" s="6">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="L43" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O43" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="12" t="s">
-        <v>87</v>
+      <c r="A44" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="B44" s="6">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D44" s="6">
         <v>1</v>
       </c>
       <c r="E44" s="6">
-        <v>25</v>
-      </c>
-      <c r="F44" s="6">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>11</v>
       </c>
       <c r="K44" s="6">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L44" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="N44" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="O44" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O44" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="6" t="s">
-        <v>88</v>
+      <c r="A45" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="B45" s="6">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D45" s="6">
         <v>1</v>
       </c>
       <c r="E45" s="6">
-        <v>0</v>
-      </c>
-      <c r="F45" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="F45" s="6">
+        <v>3</v>
+      </c>
       <c r="G45" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>11</v>
@@ -3019,7 +3025,7 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B46" s="6">
         <v>9</v>
@@ -3063,32 +3069,30 @@
       </c>
     </row>
     <row r="47" spans="1:15">
-      <c r="A47" s="9" t="s">
-        <v>90</v>
+      <c r="A47" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="B47" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="D47" s="6">
         <v>1</v>
       </c>
       <c r="E47" s="6">
-        <v>25</v>
-      </c>
-      <c r="F47" s="6">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F47" s="6"/>
       <c r="G47" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>11</v>
@@ -3110,8 +3114,8 @@
       </c>
     </row>
     <row r="48" spans="1:15">
-      <c r="A48" s="6" t="s">
-        <v>91</v>
+      <c r="A48" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="B48" s="6">
         <v>7</v>
@@ -3126,48 +3130,96 @@
         <v>25</v>
       </c>
       <c r="F48" s="6">
+        <v>3</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K48" s="6">
+        <v>20</v>
+      </c>
+      <c r="L48" s="6">
+        <v>1</v>
+      </c>
+      <c r="M48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O48" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="6">
+        <v>7</v>
+      </c>
+      <c r="C49" s="6">
+        <v>75</v>
+      </c>
+      <c r="D49" s="6">
+        <v>1</v>
+      </c>
+      <c r="E49" s="6">
+        <v>25</v>
+      </c>
+      <c r="F49" s="6">
         <v>5</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K48" s="6">
-        <v>20</v>
-      </c>
-      <c r="L48" s="6">
-        <v>1</v>
-      </c>
-      <c r="M48" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="N48" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="O48" s="10" t="s">
+      <c r="G49" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K49" s="6">
+        <v>20</v>
+      </c>
+      <c r="L49" s="6">
+        <v>1</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O49" s="10" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A39:A42">
+  <conditionalFormatting sqref="A40:A43">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2909BBE-683D-495C-B6E7-0DD3ED4DFB8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
